--- a/data/findings.xlsx
+++ b/data/findings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -422,7 +422,7 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="33" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
@@ -1911,6 +1911,1203 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, infection control, new, mater): Why Haines - Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. The wording suggests a product, catalogue, or availability change that should be verified. The signal mentions a watched hospital or private hospital group. Matched JDHG-relevant terms: patient handling, infection control, new, mater. Evidence snippet: You have no items in your shopping cart. Here are six reasons why you should choose Haines® Medical Australia for your infection control and patient handling equipment:. Haines® Medical Australia is an Australian owned and operated company that has proudly supplied Australia’s Hospitals, Healthcare and Aged Care Facilities, Health Associations and the genera</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Account follow-up</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://hainesmedical.com.au/pages/why-haines</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://hainesmedical.com.au/pages/why-haines</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (underpad, ppe, curtain, catalogue, safety): [PDF] Medical Curtains &amp; Tourniquets - ACIPC Conference</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. Matched JDHG-relevant terms: underpad, ppe, curtain, catalogue, safety. Evidence snippet: Medical Curtains &amp; Tourniquets Efficiency, Safety and Care hainesmedical.com.au Haines® Medical Australia’s Single Patient Use Tourniquet offers a simple, cost effective alternative to: • Disposable tourniquets, as they can be used for the duration of the patient’s stay, and most patients find them just as comfortable. Multi-resistant organisms (MROs), inclu</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Update sales collateral</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://acipcconference.com.au/wp-content/uploads/2022/11/ACIPC-Curtains-SPUTS-Catalogue-Nov22.pdf</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://acipcconference.com.au/wp-content/uploads/2022/11/ACIPC-Curtains-SPUTS-Catalogue-Nov22.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Arjo Australia</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, pressure injury, stretcher, new, introducing): Arjo strengthens leading position in patient handling by introducing ...</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, pressure injury, stretcher, new, introducing. Evidence snippet: Pressure Injury Prevention ... Arjo strengthens leading position in patient handling by introducing the new Maxi Move 5 patient floor lift.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us/about-us/investors/newsroom/press-releases/2025/5033470-Arjo-strengthens-leading-position-in-patient-handling-by</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us/about-us/investors/newsroom/press-releases/2025/5033470-Arjo-strengthens-leading-position-in-patient-handling-by</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, infection control, new): Buy Haines Medical Products in Australia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, infection control, new. Evidence snippet: Haines Medical Australia is an Australian managed company, specializing in infection control and safe patient handling, that has proudly supplied</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://live.joyamedicalsupplies.com.au/brands/haines</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://live.joyamedicalsupplies.com.au/brands/haines</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, infection control, new): Haines</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, infection control, new. Evidence snippet: Device Technologies is proud to work with Haines Medical Australia to deliver infection control, patient handling and environmentally friendly consumables for</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.device.com.au/our-brands/Haines</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://www.device.com.au/our-brands/Haines</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Novis Healthcare</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (pressure care): Novis Healthcare Pty Ltd</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: pressure care. Evidence snippet: Healthcare Pty Ltd - Lift, patient transfer, stationary. Alternating-pressure bed mattress overlay system. Overhead track patient lifting/transfer system (</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Compliance review</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.tga.gov.au/resources/sponsor/novis-healthcare-pty-ltd</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://www.tga.gov.au/resources/sponsor/novis-healthcare-pty-ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Novis Healthcare</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, pressure care, new, available, registered): Molift Smart 150 - Novis Healthcare®</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, pressure care, new, available, registered. Evidence snippet: Molift Smart 150 - Novis Healthcare® Novis Healthcare® 527 subscribers 1 likes 83 views 23 Aug 2022 FOR UPDATES: https://www.youtube.com/c/NovisHealthcareAU?sub_confirmation=1 --- PRODUCT AVAILABLE AT: http://novis.com.au TIMESTAMPS 00:00 - Introduction 00:05 - Features of the product 00:51 - Where and How to buy the product in Australia ____________________</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=szE3SIdwLt4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=szE3SIdwLt4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Novis Healthcare</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (pressure care, ppe, new, available): Visit our Showrooms - Novis</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: pressure care, ppe, new, available. Evidence snippet: # Visit our Showrooms. Posted by Novis Admin on **18 Nov 2025**. You are welcome to visit our showrooms, equipped with a large range of assisted daily living aids, mobility and pressure care equipment. Book an appointment with our experienced staff by calling 1300 738 885 for a full demonstration on equipment. – 20/12 Mars Road, Lane Cove West. – 3/59 Easter</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Update sales collateral</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/resources/news/lane-cove-showroom-now-open</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/resources/news/lane-cove-showroom-now-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, new): Haines Medical</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, new. Evidence snippet: Haines Medical Australia is an Australian owned company, supporting infection prevention, safe patient handling and environmental sustainability in</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://shop.aidacare.com.au/collections/haines-medical</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://shop.aidacare.com.au/collections/haines-medical</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (underpad, ppe, curtain): Haines Disposable Curtain | Antimicrobial MediCurtains® for sale from Haines Medical Australia - MedicalSearch Australia</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haines is a priority competitor for JDHG. Matched JDHG-relevant terms: underpad, ppe, curtain. Evidence snippet: All Products &gt; Hospital Equipment &amp; Supplies &gt; Hospital Disposable Curtain. # Haines - Disposable Curtain | Antimicrobial MediCurtains®. ## 3 widths (2.5m to 7.5m), standard 2m drop (or custom cut), 2 hook types (roller or S style), 8 standard colours (including neutrals, blue, lilac and teal) and 3 patterns. Haines® Antimicrobial MediCurtains® are designed </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.medicalsearch.com.au/haines-disposable-curtain-antimicrobial-medicurtains/p/172553</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://www.medicalsearch.com.au/haines-disposable-curtain-antimicrobial-medicurtains/p/172553</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Patient Handling</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, hoist, sling, slide sheet, trolley): Slide &amp; Turn Hoist Sheet - Use a hoist to turn a patient</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, hoist, sling, slide sheet, trolley, new. Evidence snippet: Slide &amp; Turn Hoist Sheet - Use a hoist to turn a patient. # Slide &amp; Turn Hoist Sheet. The Slide &amp; Turn Hoist Sheet is a great way of getting a hoist to do the turning, rather than the carer. This product is an alternative to the Slide &amp; Turn Sheet. * Use a trolley hoist or ceiling hoist to do the turning. * **Slide &amp; Turn Hoist Sheet:** Standard design with </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.pelicanmanufacturing.com.au/product/slide-turn-hoist-sheet</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://www.pelicanmanufacturing.com.au/product/slide-turn-hoist-sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Patient Handling</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, hoist, lifter, sling, slide sheet): Patient Hoists &amp; Slings | Patient Lifting Equipment for Disabled &amp; Elderly - Page 1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, hoist, lifter, sling, slide sheet, new. Evidence snippet: By utilising patient lifts, slings, and ceiling hoists, the need for strenuous manual lifting and handling is minimised. A patient hoist or sling is a free-standing piece of equipment created to support an individual being transported from one place to another. What types of hoists and slings does Patient Handling offer? We offer a range of products includin</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.patienthandling.com.au/c/hoists-slings</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://www.patienthandling.com.au/c/hoists-slings</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Etac</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (positioning, sling, stretcher, new, catalogue): Molift</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The wording suggests a product, catalogue, or availability change that should be verified. The signal mentions a watched hospital or private hospital group. Matched JDHG-relevant terms: positioning, sling, stretcher, new, catalogue, mater. Evidence snippet: YEAR User name / Namn MONTH Barcode according to EAN number Molift RgoSling XXXXXXXX EAN NUMBER (01)0XXXXXXXXXXXXX DK: HMI XXXXX TUMBLEDRY MAX 50ºC /122ºF 60-80ºC 140-176ºF NORMAL DO NOT IRON DO NOT DRYCLEAN DO NOT BLEACH Item no: XXXXXXX Material: Polyester, polyethylene Etac AS, Etac Supply Gjøvik Hadelandsveien 2 N-2816 Gjøvik, Norway Size X (21)XXXXXXXX </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Account follow-up</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.imr.net.au/wp-content/uploads/2022/05/Molift-Catalogue.pdf</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.imr.net.au/wp-content/uploads/2022/05/Molift-Catalogue.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HoverTech</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (positioning, lateral transfer, air-assisted, air assisted, infection control): HoverTech International - HoverMatt Air Transfer System</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: positioning, lateral transfer, air-assisted, air assisted, infection control, safety. Evidence snippet: HoverMatt, the number one choice of hospitals for lateral patient transfers, further addresses infection control and reprocessing concerns with the **HoverMatt Single Patient Use** Air Transfer System. This inflatable transfer mattress works just like the reusable HoverMatt air transfer system; the mattress - and the patient - float on a cushion of air. By v</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>http://hovertech.com.au/hovermatt-spu.html</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>http://hovertech.com.au/hovermatt-spu.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Arjo Australia</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, positioning, lateral transfer, hoist, sling): In bed and lateral transfer slings for medical hoists - Arjo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: patient handling, positioning, lateral transfer, hoist, sling, stretcher. Evidence snippet: Slings for lateral transfer, repositioning in bed, prone positioning and limb lifting. Used in combination with a ceiling or passive floor lift.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-au/products/patient-handling/slings/in-bed-and-lateral-transfer-slings</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-au/products/patient-handling/slings/in-bed-and-lateral-transfer-slings</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Aidacare</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, hoist, sling, hospital bed, contract): Manual Handling - Easy &amp; Safe Transfers | Aidacare</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: patient handling, hoist, sling, hospital bed, contract. Evidence snippet: # Manual Handling. * Manual lifting and moving of patients can be unsafe and lead to injuries. * Special equipment should be used for strain-free handling and transfers. * Aidacare offers a wide range of patient handling equipment. * Equipment designed to ensure easy and safe transfers for both caregivers and patients. * Selection includes lifts, hoists, sli</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Add to tender intelligence</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.aidacare.co.nz/products-nz/manual-handling-transfer</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.aidacare.co.nz/products-nz/manual-handling-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Patient Handling</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, hoist, sling, slide sheet, new): Slide Sheets - Novis</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, hoist, sling, slide sheet, new. Evidence snippet: Slide Sheets are an essential solution for healthcare professionals and caregivers seeking a safe and efficient way to move patients. Immedia MultiGlide Nylon Handling Gloves. next icon Product Details Immedia MultiGlide Nylon Slide Sheet with Handles. ## Immedia MultiGlide Nylon Slide Sheet with Handles. next icon Product Details Immedia MultiGlide SG Nylon</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/category/products/patient-handling-2/slide-sheets</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/category/products/patient-handling-2/slide-sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Patient Handling</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, hoist, sling, slide sheet, new): Slings - Patient Lifting Hoists</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, hoist, sling, slide sheet, new. Evidence snippet: We sell a wide range of superior lift slings in a range of sizes, fabrics and models to suit every patient's needs, younger or elderly.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.aidacare.com.au/products/manual-handling-transfer/slings-patient-lifting-hoists</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.aidacare.com.au/products/manual-handling-transfer/slings-patient-lifting-hoists</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HoverTech</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, positioning, air-assisted, air assisted, safety): HoverTech International - Australia</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: patient handling, positioning, air-assisted, air assisted, safety. Evidence snippet: HoverMatt Air Transfer System - Reusable &amp; Single Patient Use | HoverMatt MINI. HoverJack Air Patient Lift | HoverJack Evacuation II. ##### **Australian Site**. HoverTech International is the world leader in air-assisted safe patient handling. HoverTech’s complete portfolio of patient handling, repositioning, and handling products reduces caregiver injury, w</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>http://hovertech.com.au</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>http://hovertech.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HoverTech</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (positioning, lateral transfer, air assisted, sling, mater): Lateral Transfers - HoverTech International</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>The signal mentions a watched hospital or private hospital group. Matched JDHG-relevant terms: positioning, lateral transfer, air assisted, sling, mater. Evidence snippet: # Lateral Transfers. Lateral patient transfers are performed in every hospital unit. Using advanced air technology, the HoverMatt® and HoverSling® products can laterally transfer patients up to 1200 lbs with as little as two caregivers. Patients will have a safe, comfortable and dignified experience on all of HoverTech’s lateral transfer and positioning devi</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Account follow-up</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://hovertechinternational.com/solutions/lateral-transfers</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://hovertechinternational.com/solutions/lateral-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HoverTech</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (positioning, air-assisted, new): Reduce work-related injuries for caregivers</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: positioning, air-assisted, new. Evidence snippet: The HoverMatt air-assisted transfer system includes a range of multifunctional products that make patient transfers, boosting and repositioning easier — at the</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.etac.com/en-gb/uk/about-us/news-and-social-media/newsroom/2024/hovertech---reduces-work-related-injuries</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.etac.com/en-gb/uk/about-us/news-and-social-media/newsroom/2024/hovertech---reduces-work-related-injuries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/findings.xlsx
+++ b/data/findings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -422,7 +422,7 @@
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="33" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
@@ -1911,6 +1911,1431 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (underpad, ppe, curtain, infection control, safety): Why Disposable Hospital Curtains Are Revolutionizing Infection Control?</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. The signal mentions a watched hospital or private hospital group. Matched JDHG-relevant terms: underpad, ppe, curtain, infection control, safety, mater. Evidence snippet: At HAIGuard™, we specialize in providing healthcare facilities with high-quality, disposable hospital curtains designed to enhance infection control and patient safety. Our curtains are made from durable, antimicrobial materials that offer superior protection against bacteria, viruses, and other pathogens. We understand the importance of cleanliness in healt</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Account follow-up</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://haiguard.com/blog/why-disposable-hospital-curtains-are-revolutionizing-infection-control</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://haiguard.com/blog/why-disposable-hospital-curtains-are-revolutionizing-infection-control</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Patient Handling</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, hoist, sling, slide sheet, new): Planning vital when using patient handling slings</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, hoist, sling, slide sheet, new, safety. Evidence snippet: Patient handling slings are a vital resource to make patient transfers safer for both staff and patients, but processes must be adhered to.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Compliance review</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.tga.gov.au/news/safety-updates/planning-vital-when-using-patient-handling-slings</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://www.tga.gov.au/news/safety-updates/planning-vital-when-using-patient-handling-slings</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, positioning, sling, transfer board, slide sheet): Why Haines - Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haines is a priority competitor for JDHG. The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, positioning, sling, transfer board, slide sheet, infection control, new. Evidence snippet: My Account Login Haines Medical Australia CALL US NOW 1300 HAINES 0item(s) You have no items in your shopping cart. Start typing to see products you are looking for. Haines Medical Australia Home Shop Patient Handling + Slide Sheets &amp; Tubes - Slide Sheets - Slide Tubes - Transfer Sheets + Slings &amp; Straps - Patient Slings - Positioning Straps + Transfer Mats </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://hainesmedical.com.au/pages/why-haines</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://hainesmedical.com.au/pages/why-haines</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Arjo Australia</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, pressure injury, stretcher, new, launch): Arjo strengthens leading position in patient handling by ...</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, pressure injury, stretcher, new, launch, safety. Evidence snippet: Arjo, a global leader in medical device technology, today announces the launch of Maxi Move 5®, the latest generation of one of the company’s best-selling products.The new top-of-the-line mobile patient floor lift features several innovative technical solutions designed to help reduce caregiver injuries and optimize efficiencies in care situations. [...] “Pa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us/about-us/investors/newsroom/press-releases/2025/5033470-Arjo-strengthens-leading-position-in-patient-handling-by</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us/about-us/investors/newsroom/press-releases/2025/5033470-Arjo-strengthens-leading-position-in-patient-handling-by</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Patient Handling</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, hoist, sling, slide sheet, ppe): Slide &amp; Turn Hoist Sheet - Use a hoist to turn a patient</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. The signal mentions a watched hospital or private hospital group. Matched JDHG-relevant terms: patient handling, hoist, sling, slide sheet, ppe, theatre, new, mater. Evidence snippet: Slide &amp; Turn Hoist Sheet Slide &amp; Turn Hoist Sheet Slide &amp; Turn Hoist Sheet # Slide &amp; Turn Hoist Sheet Units of Measurement: Each SKU: 509H-VARIOUS Categories: Bariatric Equipment, Hoist Slings Equipment, Manual Handling Equipment, Theatre &amp; Post Operative Care From AUD $115.00 ### Description #### WHAT IS THIS PRODUCT? [...] ## Bed Slide Sheet Slippery, brea</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Account follow-up</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.pelicanmanufacturing.com.au/product/slide-turn-hoist-sheet</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://www.pelicanmanufacturing.com.au/product/slide-turn-hoist-sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, infection control, new): Haines Medical Australia | Infection Contol and Patient Handling | Our Brands</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, infection control, new. Evidence snippet: Haines Medical Australia supports infection prevention, patient handling and environmental sustainability in Australian healthcare. It has proudly supplied Australian hospitals, healthcare facilities, aged care facilities and the general community with healthcare supplies since 1974. At the heart of Haines is the Solutions Lab; a ‘product problem-solving ser</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.device.com.au/our-brands/Haines</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://www.device.com.au/our-brands/Haines</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (underpad, ppe, curtain, infection control): Medical Curtains | Haines Healthcare Privacy Curtains</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. Matched JDHG-relevant terms: underpad, ppe, curtain, infection control. Evidence snippet: Healthcare privacy curtains help create safe patient spaces while supporting infection control protocols and efficient ward management. Modern disposable and</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://medisa.com.au/collections/medical-curtains</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://medisa.com.au/collections/medical-curtains</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Novis Healthcare</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (positioning, hoist, pressure care, pressure injury, new): In-bed Systems</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: positioning, hoist, pressure care, pressure injury, new, available. Evidence snippet: It is designed to be left in place under the patient and makes repositioning easier, reducing the risk of injury for carers and promotes a higher quality of care for patients. • 500 kg (78 stone) Safe Working Load • Time-saving - stays on the bed, ready for use when needed. • Maximum comfort - no webbing under the patient reducing the risk of pressure injury</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/wp-content/uploads/2023/04/Immedia-In-Bed-Systems-Video-links.pdf</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/wp-content/uploads/2023/04/Immedia-In-Bed-Systems-Video-links.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Etac</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (new, launch, launched, available): Molift Smart 150</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: new, launch, launched, available. Evidence snippet: Molift Smart 150 is designed for transfers over short distances, such as between the bed and a chair, or into the bathroom. The lift is ideal for home care but can be used in any care setting. The Molift Smart 150 is foldable in one piece without using any tools making it great for traveling and easy storage. A soft travel bag and a hard shell suitcase are a</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.etac.com/en-us/us/products/patient-handling/mobile-lifts/molift-smart-150</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://www.etac.com/en-us/us/products/patient-handling/mobile-lifts/molift-smart-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HoverTech</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, positioning, air assisted, sling, brochure): Elevate Your Standard of Care - HoverTech International</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: patient handling, positioning, air assisted, sling, brochure, safety. Evidence snippet: One Product. Many Uses. The breathable HoverMatt® Single-Patient Use (SPU) Air Transfer Mattress makes patient transfers, boosting, positioning and proning easier, while protecting caregiver safety. A cushion of air beneath the inflated HoverMatt SPU reduces the force required to move a patient by 80-90%, enabling caregivers to safely transfer patients witho</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Update sales collateral</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://hovertechinternational.com/elevate-your-standard-of-care-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://hovertechinternational.com/elevate-your-standard-of-care-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HoverTech</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, positioning, lateral transfer, air-assisted, new): Etac invests in HoverTech, a US patient handling company</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, positioning, lateral transfer, air-assisted, new. Evidence snippet: HoverTech is a US leader in air-assisted patient handling technologies, focusing on devices for lateral transfer and repositioning. The company’s sales in 2018 totalled approximately USD 100 million. The company is owned by its founder Dave Davis and family, and is based in Allentown, Pennsylvania. [...] “This is a strategically important investment that sig</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.etac.com/about-us/news--social-media/Newsroom/2019/etac-invests-in-hovertech-a-us-patient-handling-company</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://www.etac.com/about-us/news--social-media/Newsroom/2019/etac-invests-in-hovertech-a-us-patient-handling-company</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Haines Medical Australia</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, new): Haines Medical Australia: Patient Handling &amp; Infection ...</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Haines is a priority competitor for JDHG. The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, new. Evidence snippet: Haines® Medical Australia is an Australian owned company, supporting infection prevention, safe patient handling. supplies since 1974.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.medicalsearch.com.au/haines-medical-australia/s/54653</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://www.medicalsearch.com.au/haines-medical-australia/s/54653</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Arjo Australia</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, new, launch, introducing): Patient Handling Equipment – Lifts for easy transfer | Arjo</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, new, launch, introducing. Evidence snippet: Every healthcare facility is unique, with diverse patient and caregiver needs that demand flexible solutions. Enabling single-handed care with the all new Maxi Move® 5 ### Meeting your versatility needs with Maxi Move® 5 Each healthcare facility has its own unique challenges. Meeting your versatility needs with Maxi Move® 5 ### Introducing Maxi Move® 5 – a n</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us/products/patient-handling</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us/products/patient-handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Aidacare</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (hoist, lifter, pressure care, new, product alert): Home | Aidacare</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: hoist, lifter, pressure care, new, product alert. Evidence snippet: print online@aidacare.com.au 1300 133 120 Skip to Navigation Skip to Content Tailor Your Online Experience Aidacare Solutions Aidacare Solutions Online Shop Online Shop Product Alert: User Manual Enhancement for Aidacare A205 Aluminium Patient Lifter and Aspire Active Air 8 Pressure Care Air Mattress - Read More Aidacare 1300 133 120 ") Return Credit / Produ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.aidacare.com.au</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://www.aidacare.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Novis Healthcare</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (hoist, sling, pressure injury, new, mater): Brands - Novis</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. The signal mentions a watched hospital or private hospital group. Matched JDHG-relevant terms: hoist, sling, pressure injury, new, mater. Evidence snippet: Molift is part of the Etac Group, a market-leading developer of mobility products. Molift products are renowned for their ergonomic architecture, function and product design providing five-star services to assist those living with limited or restricted mobility. Molift products are known for their simple and innovative design, quality, reliability and functi</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Account follow-up</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/category/brands</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://novis.com.au/category/brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Patient Handling</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (hoist, lifter, sling, available): How To Use A Leg Lifter to Help Get In &amp; Out of Bed | How To Guides</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: hoist, lifter, sling, available. Evidence snippet: 1. Sit on the side of the bed. 2. Position the open foot loop of the leg lifter over the foot. 3. Lean forward and hold the lowest hand loop available. 4. Utilize the leg lifter to lift and reposition the leg without bending over. Depending on the user’s needs and preferences, a leg lifter can be employed to lift either one or both legs. This versatility mak</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Update sales collateral</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.patienthandling.com.au/resources/how-to-use-a-leg-lifter</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.patienthandling.com.au/resources/how-to-use-a-leg-lifter</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HoverTech</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, positioning, lateral transfer, air assisted, sling): Lateral Transfers - HoverTech International</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: patient handling, positioning, lateral transfer, air assisted, sling, safety. Evidence snippet: Patients will have a safe, comfortable and dignified experience on all of HoverTech’s lateral transfer and positioning devices. The patient safety strap and patented cradling effect will help individuals feel secure and provide comfort during lateral transfers. Friction and skin shear are greatly reduced, as the patient is transferred from surface to surface</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://hovertechinternational.com/solutions/lateral-transfers</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://hovertechinternational.com/solutions/lateral-transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Anetic Aid</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (stretcher, trolley, theatre, new, safety): Compact, lightweight &amp; robust patient stretchers | AneticAid &lt;anajcvqpjga /&gt; US</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: stretcher, trolley, theatre, new, safety. Evidence snippet: 'By using Day Surgery Trolleys rather than operating tables, we are saving a huge amount of time in theatre turnaround. We have increased our patient throughput by approximately 3-4 patients per day on a three session list. It directly benefits my team with a reduction in patient moving and handling, as well as improving patient safety by reducing the amount</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://aneticaid.com/us</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://aneticaid.com/us</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Anetic Aid</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (stretcher, trolley, theatre, new, safety): [PDF] 60601-2-52 and the Anetic Aid range of patient stretchers - DigitalOcean</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: stretcher, trolley, theatre, new, safety. Evidence snippet: The QA3™ Patient Stretcher system is designed and manufactured in compliance with (but not limited to): • BS 5402 - Patient Trolleys • BS EN 60601-2-52 - Medical Electrical Equipment. Particular requirements for basic safety and essential performance of medical beds The QA4™ Mobile Surgery System is designed and manufactured in compliance with (but not limit</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://aneticaid.ams3.digitaloceanspaces.com/anetic_aid_60601-2-52-flyer-final-digital.pdf</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://aneticaid.ams3.digitaloceanspaces.com/anetic_aid_60601-2-52-flyer-final-digital.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lateral Medical</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient positioning, positioning, infection control, theatre, new): About Us - Medical Supplies Australia - Medical Equipment</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient positioning, positioning, infection control, theatre, new. Evidence snippet: Lateral Medical is an Australian-owned company that specialises in providing medical ... Infection Control &amp; OHS; Patient Positioning; Obstetrics and Gynaecology</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://lateralmedical.com/about-us</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://lateralmedical.com/about-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Lateral Medical</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (ppe, infection control, theatre, surgical, new): Sterile Surgical Covers - Quest Surgical</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: ppe, infection control, theatre, surgical, new. Evidence snippet: Quest Surgical is a trusted Australian medical supply company supplying Sterile Surgical Covers, operating theatre consumables, imaging equipment covers, and infection control products to hospitals and healthcare providers across South East Queensland and Australia. [...] Conforming Bandages ## Defries Industries Crepe and Conforming Bandages ## Ask a surgic</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.questsurgical.com.au/product/sterile-surgical-covers</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.questsurgical.com.au/product/sterile-surgical-covers</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Arjo Australia</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, infection control, new, safety): Global supplier of medical devices &amp; medical solutions | Arjo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: patient handling, infection control, new, safety. Evidence snippet: Discover how the upgraded AirPal® harnesses air’s invisible force to lighten the load of care – using precise, controlled airflow to help caregivers reposition patients safely, comfortably, and efficiently. Experience the power of Air, experience the power of AirPal. Discover More ### ​The next generation of patient handling is here​ See how Maxi Move® 5 imp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Review product overlap</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Arjo Australia</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, positioning, lateral transfer, hoist, sling): In bed and lateral transfer slings for medical hoists</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Matched JDHG-relevant terms: patient handling, positioning, lateral transfer, hoist, sling, stretcher. Evidence snippet: Patient lateral transfer and repositioning slings in a supine position. Safe and comfortable sling solutions for hospitals, nursing homes and</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-au/products/patient-handling/slings/in-bed-and-lateral-transfer-slings</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.arjo.com/en-au/products/patient-handling/slings/in-bed-and-lateral-transfer-slings</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Novis Healthcare</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (patient handling, pressure care, available, mater): Novis Healthcare - Pressure Care and Patient Handling Products Australia</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. The signal mentions a watched hospital or private hospital group. Matched JDHG-relevant terms: patient handling, pressure care, available, mater. Evidence snippet: Novis AreaCare Hospital Mattress Extension Double Layer Extension is ideal for users who are at-risk for pressure sores and ulcers, especially in the high-risk heel zone. This two-layer, 200 mm... Novis AreaCare Plus Triple Layer Hospital Mattress Novis #### Novis AreaCare Plus Triple Layer Hospital Mattress [...] Novis AreaCare Plus Triple Layer King Single</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Account follow-up</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.medisupplies.com.au/novis</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.medisupplies.com.au/novis</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Medium priority</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Novis Healthcare</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>patient handling and positioning devices; theatre consumables; hospital consumables; underpads</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Possible relevant market signal surfaced (new, introducing, catalogue): Introducing the ProCair Prime Advanced Mattress When it comes ...</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The wording suggests a product, catalogue, or availability change that should be verified. Matched JDHG-relevant terms: new, introducing, catalogue. Evidence snippet: ... new Novis Product Catalogue via the link in bio. ... novis atsa independent living expo THE DOME BetterLiving molift by Etac Novis Healthcare is</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Update sales collateral</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Low-Medium: Rule-based triage because Claude did not run. Claude API failed for models: claude-3-5-haiku-latest, claude-3-5-haiku-20241022, claude-3-haiku-20240307</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Competitor website / web search</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DJDPdmKo3JK</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DJDPdmKo3JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
